--- a/public/exports-with-coowners/29189757.xlsx
+++ b/public/exports-with-coowners/29189757.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">

--- a/public/exports-with-coowners/29189757.xlsx
+++ b/public/exports-with-coowners/29189757.xlsx
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">

--- a/public/exports-with-coowners/29189757.xlsx
+++ b/public/exports-with-coowners/29189757.xlsx
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
